--- a/Datos limpios/Pricing diario/2025/Soja.xlsx
+++ b/Datos limpios/Pricing diario/2025/Soja.xlsx
@@ -10929,298 +10929,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100D6CA5EAACE9DA04D9E421A617A76D009" ma:contentTypeVersion="19" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="854b0670eee28d8fa271d4f22cb9c97d">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="77131357-5c03-45fa-a80b-b9111bb46cb1" xmlns:ns3="d3f11db4-a96c-41b4-b8ec-902c72f52048" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b486ba09ce8a2fb19cc660d7edf32df4" ns2:_="" ns3:_="">
-    <xsd:import namespace="77131357-5c03-45fa-a80b-b9111bb46cb1"/>
-    <xsd:import namespace="d3f11db4-a96c-41b4-b8ec-902c72f52048"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:_Flow_SignoffStatus" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="77131357-5c03-45fa-a80b-b9111bb46cb1" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="14" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="15" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="17" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="_Flow_SignoffStatus" ma:index="20" nillable="true" ma:displayName="Estado de aprobación" ma:internalName="Estado_x0020_de_x0020_aprobaci_x00f3_n">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="21" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="6ab20cb4-9c0f-41d2-89f3-02c382a657d6" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="25" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="26" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d3f11db4-a96c-41b4-b8ec-902c72f52048" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="24" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ac6aff7b-77d9-4645-af3f-7b0008d975fa}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="d3f11db4-a96c-41b4-b8ec-902c72f52048">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="77131357-5c03-45fa-a80b-b9111bb46cb1" xsi:nil="true"/>
-    <TaxCatchAll xmlns="d3f11db4-a96c-41b4-b8ec-902c72f52048" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="77131357-5c03-45fa-a80b-b9111bb46cb1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{700EB4C9-DB62-484C-A47F-8A072D8773AC}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93F4FCEB-5CD6-4907-B77D-0AD5C8C310E7}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCA18D3F-1311-4A0F-B68E-2D979B98A13E}"/>
 </file>
--- a/Datos limpios/Pricing diario/2025/Soja.xlsx
+++ b/Datos limpios/Pricing diario/2025/Soja.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K285"/>
+  <dimension ref="A1:K310"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -9636,16 +9636,16 @@
         <v>45922</v>
       </c>
       <c r="B251">
-        <v>403402.03</v>
+        <v>402766.9</v>
       </c>
       <c r="C251">
         <v>1430.59</v>
       </c>
       <c r="D251">
-        <v>4120.82</v>
+        <v>4755.95</v>
       </c>
       <c r="E251">
-        <v>400711.8</v>
+        <v>399441.54</v>
       </c>
       <c r="F251">
         <v>81166.00999999999</v>
@@ -9660,7 +9660,7 @@
         <v>81166.00999999999</v>
       </c>
       <c r="J251">
-        <v>481877.8100000001</v>
+        <v>480607.55</v>
       </c>
       <c r="K251" t="inlineStr">
         <is>
@@ -9713,13 +9713,13 @@
         <v>1349975.32</v>
       </c>
       <c r="C253">
-        <v>51357.16</v>
+        <v>51338.7</v>
       </c>
       <c r="D253">
         <v>13808.88</v>
       </c>
       <c r="E253">
-        <v>1387523.6</v>
+        <v>1387505.14</v>
       </c>
       <c r="F253">
         <v>189090.05</v>
@@ -9734,7 +9734,7 @@
         <v>186900.8</v>
       </c>
       <c r="J253">
-        <v>1574424.4</v>
+        <v>1574405.94</v>
       </c>
       <c r="K253" t="inlineStr">
         <is>
@@ -9747,16 +9747,16 @@
         <v>45925</v>
       </c>
       <c r="B254">
-        <v>678916.88</v>
+        <v>678766.88</v>
       </c>
       <c r="C254">
-        <v>11052.16</v>
+        <v>11144.45</v>
       </c>
       <c r="D254">
         <v>17291.82</v>
       </c>
       <c r="E254">
-        <v>672677.2200000001</v>
+        <v>672619.51</v>
       </c>
       <c r="F254">
         <v>164814.14</v>
@@ -9771,7 +9771,7 @@
         <v>164739.89</v>
       </c>
       <c r="J254">
-        <v>837417.1100000001</v>
+        <v>837359.4</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
@@ -9969,16 +9969,16 @@
         <v>45931</v>
       </c>
       <c r="B260">
-        <v>265462.51</v>
+        <v>265338.71</v>
       </c>
       <c r="C260">
-        <v>3191.67</v>
+        <v>3311.63</v>
       </c>
       <c r="D260">
         <v>2207</v>
       </c>
       <c r="E260">
-        <v>266447.18</v>
+        <v>266443.34</v>
       </c>
       <c r="F260">
         <v>113926.04</v>
@@ -9993,7 +9993,7 @@
         <v>113926.04</v>
       </c>
       <c r="J260">
-        <v>380373.22</v>
+        <v>380369.38</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
@@ -10006,16 +10006,16 @@
         <v>45932</v>
       </c>
       <c r="B261">
-        <v>294123.49</v>
+        <v>293123.49</v>
       </c>
       <c r="C261">
-        <v>3275.92</v>
+        <v>4128.57</v>
       </c>
       <c r="D261">
         <v>5476.690000000001</v>
       </c>
       <c r="E261">
-        <v>291922.72</v>
+        <v>291775.37</v>
       </c>
       <c r="F261">
         <v>78989.92999999999</v>
@@ -10030,7 +10030,7 @@
         <v>78989.92999999999</v>
       </c>
       <c r="J261">
-        <v>370912.65</v>
+        <v>370765.3</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
@@ -10046,13 +10046,13 @@
         <v>334016.98</v>
       </c>
       <c r="C262">
-        <v>2713.15</v>
+        <v>2713.89</v>
       </c>
       <c r="D262">
         <v>2110</v>
       </c>
       <c r="E262">
-        <v>334620.13</v>
+        <v>334620.87</v>
       </c>
       <c r="F262">
         <v>88553.56</v>
@@ -10067,7 +10067,7 @@
         <v>88403.56</v>
       </c>
       <c r="J262">
-        <v>423023.69</v>
+        <v>423024.43</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
@@ -10154,16 +10154,16 @@
         <v>45936</v>
       </c>
       <c r="B265">
-        <v>198291.63</v>
+        <v>198231.63</v>
       </c>
       <c r="C265">
         <v>4509.5</v>
       </c>
       <c r="D265">
-        <v>18978.12</v>
+        <v>19038.12</v>
       </c>
       <c r="E265">
-        <v>183823.01</v>
+        <v>183703.01</v>
       </c>
       <c r="F265">
         <v>62297.03</v>
@@ -10178,7 +10178,7 @@
         <v>43297.03</v>
       </c>
       <c r="J265">
-        <v>227120.04</v>
+        <v>227000.04</v>
       </c>
       <c r="K265" t="inlineStr">
         <is>
@@ -10894,33 +10894,958 @@
         <v>45957</v>
       </c>
       <c r="B285">
-        <v>2677.84</v>
+        <v>50604.28</v>
       </c>
       <c r="C285">
-        <v>0</v>
+        <v>178.36</v>
       </c>
       <c r="D285">
-        <v>0</v>
+        <v>5342.57</v>
       </c>
       <c r="E285">
-        <v>2677.84</v>
+        <v>45440.07</v>
       </c>
       <c r="F285">
-        <v>0</v>
+        <v>11333.09</v>
       </c>
       <c r="G285">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H285">
         <v>0</v>
       </c>
       <c r="I285">
-        <v>0</v>
+        <v>11413.09</v>
       </c>
       <c r="J285">
-        <v>2677.84</v>
+        <v>56853.16</v>
       </c>
       <c r="K285" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2">
+        <v>45958</v>
+      </c>
+      <c r="B286">
+        <v>96859.46000000001</v>
+      </c>
+      <c r="C286">
+        <v>377.09</v>
+      </c>
+      <c r="D286">
+        <v>4360</v>
+      </c>
+      <c r="E286">
+        <v>92876.55</v>
+      </c>
+      <c r="F286">
+        <v>25867.29</v>
+      </c>
+      <c r="G286">
+        <v>0</v>
+      </c>
+      <c r="H286">
+        <v>0</v>
+      </c>
+      <c r="I286">
+        <v>25867.29</v>
+      </c>
+      <c r="J286">
+        <v>118743.84</v>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2">
+        <v>45959</v>
+      </c>
+      <c r="B287">
+        <v>44558.48</v>
+      </c>
+      <c r="C287">
+        <v>356.56</v>
+      </c>
+      <c r="D287">
+        <v>800</v>
+      </c>
+      <c r="E287">
+        <v>44115.04</v>
+      </c>
+      <c r="F287">
+        <v>14436.78</v>
+      </c>
+      <c r="G287">
+        <v>0</v>
+      </c>
+      <c r="H287">
+        <v>0</v>
+      </c>
+      <c r="I287">
+        <v>14436.78</v>
+      </c>
+      <c r="J287">
+        <v>58551.82</v>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2">
+        <v>45960</v>
+      </c>
+      <c r="B288">
+        <v>46843.74</v>
+      </c>
+      <c r="C288">
+        <v>1033.43</v>
+      </c>
+      <c r="D288">
+        <v>120</v>
+      </c>
+      <c r="E288">
+        <v>47757.17</v>
+      </c>
+      <c r="F288">
+        <v>8068.94</v>
+      </c>
+      <c r="G288">
+        <v>0</v>
+      </c>
+      <c r="H288">
+        <v>30</v>
+      </c>
+      <c r="I288">
+        <v>8038.94</v>
+      </c>
+      <c r="J288">
+        <v>55796.11</v>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2">
+        <v>45961</v>
+      </c>
+      <c r="B289">
+        <v>35568</v>
+      </c>
+      <c r="C289">
+        <v>576.14</v>
+      </c>
+      <c r="D289">
+        <v>566.5700000000001</v>
+      </c>
+      <c r="E289">
+        <v>35577.57</v>
+      </c>
+      <c r="F289">
+        <v>12830.54</v>
+      </c>
+      <c r="G289">
+        <v>0</v>
+      </c>
+      <c r="H289">
+        <v>0</v>
+      </c>
+      <c r="I289">
+        <v>12830.54</v>
+      </c>
+      <c r="J289">
+        <v>48408.11</v>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2">
+        <v>45962</v>
+      </c>
+      <c r="B290">
+        <v>1260.8</v>
+      </c>
+      <c r="C290">
+        <v>0</v>
+      </c>
+      <c r="D290">
+        <v>0</v>
+      </c>
+      <c r="E290">
+        <v>1260.8</v>
+      </c>
+      <c r="F290">
+        <v>954.34</v>
+      </c>
+      <c r="G290">
+        <v>0</v>
+      </c>
+      <c r="H290">
+        <v>0</v>
+      </c>
+      <c r="I290">
+        <v>954.34</v>
+      </c>
+      <c r="J290">
+        <v>2215.14</v>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2">
+        <v>45963</v>
+      </c>
+      <c r="B291">
+        <v>0</v>
+      </c>
+      <c r="C291">
+        <v>0</v>
+      </c>
+      <c r="D291">
+        <v>0</v>
+      </c>
+      <c r="E291">
+        <v>0</v>
+      </c>
+      <c r="F291">
+        <v>13081.43</v>
+      </c>
+      <c r="G291">
+        <v>0</v>
+      </c>
+      <c r="H291">
+        <v>0</v>
+      </c>
+      <c r="I291">
+        <v>13081.43</v>
+      </c>
+      <c r="J291">
+        <v>13081.43</v>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2">
+        <v>45964</v>
+      </c>
+      <c r="B292">
+        <v>60670.65</v>
+      </c>
+      <c r="C292">
+        <v>1084</v>
+      </c>
+      <c r="D292">
+        <v>0</v>
+      </c>
+      <c r="E292">
+        <v>61754.65</v>
+      </c>
+      <c r="F292">
+        <v>19984.25</v>
+      </c>
+      <c r="G292">
+        <v>0</v>
+      </c>
+      <c r="H292">
+        <v>0</v>
+      </c>
+      <c r="I292">
+        <v>19984.25</v>
+      </c>
+      <c r="J292">
+        <v>81738.89999999999</v>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2">
+        <v>45965</v>
+      </c>
+      <c r="B293">
+        <v>100964.81</v>
+      </c>
+      <c r="C293">
+        <v>120</v>
+      </c>
+      <c r="D293">
+        <v>484</v>
+      </c>
+      <c r="E293">
+        <v>100600.81</v>
+      </c>
+      <c r="F293">
+        <v>7087.76</v>
+      </c>
+      <c r="G293">
+        <v>0</v>
+      </c>
+      <c r="H293">
+        <v>0</v>
+      </c>
+      <c r="I293">
+        <v>7087.76</v>
+      </c>
+      <c r="J293">
+        <v>107688.57</v>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2">
+        <v>45966</v>
+      </c>
+      <c r="B294">
+        <v>34627.79</v>
+      </c>
+      <c r="C294">
+        <v>1779.98</v>
+      </c>
+      <c r="D294">
+        <v>2006.73</v>
+      </c>
+      <c r="E294">
+        <v>34401.04</v>
+      </c>
+      <c r="F294">
+        <v>8469.5</v>
+      </c>
+      <c r="G294">
+        <v>0</v>
+      </c>
+      <c r="H294">
+        <v>0</v>
+      </c>
+      <c r="I294">
+        <v>8469.5</v>
+      </c>
+      <c r="J294">
+        <v>42870.54</v>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2">
+        <v>45967</v>
+      </c>
+      <c r="B295">
+        <v>97021.96000000001</v>
+      </c>
+      <c r="C295">
+        <v>9595.15</v>
+      </c>
+      <c r="D295">
+        <v>0</v>
+      </c>
+      <c r="E295">
+        <v>106617.11</v>
+      </c>
+      <c r="F295">
+        <v>3219.16</v>
+      </c>
+      <c r="G295">
+        <v>1400</v>
+      </c>
+      <c r="H295">
+        <v>0</v>
+      </c>
+      <c r="I295">
+        <v>4619.16</v>
+      </c>
+      <c r="J295">
+        <v>111236.27</v>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2">
+        <v>45968</v>
+      </c>
+      <c r="B296">
+        <v>121284.69</v>
+      </c>
+      <c r="C296">
+        <v>3058.85</v>
+      </c>
+      <c r="D296">
+        <v>6340</v>
+      </c>
+      <c r="E296">
+        <v>118003.54</v>
+      </c>
+      <c r="F296">
+        <v>9192.879999999999</v>
+      </c>
+      <c r="G296">
+        <v>800</v>
+      </c>
+      <c r="H296">
+        <v>132.8</v>
+      </c>
+      <c r="I296">
+        <v>9860.08</v>
+      </c>
+      <c r="J296">
+        <v>127863.62</v>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2">
+        <v>45969</v>
+      </c>
+      <c r="B297">
+        <v>1359.4</v>
+      </c>
+      <c r="C297">
+        <v>0</v>
+      </c>
+      <c r="D297">
+        <v>10.78</v>
+      </c>
+      <c r="E297">
+        <v>1348.62</v>
+      </c>
+      <c r="F297">
+        <v>30</v>
+      </c>
+      <c r="G297">
+        <v>0</v>
+      </c>
+      <c r="H297">
+        <v>0</v>
+      </c>
+      <c r="I297">
+        <v>30</v>
+      </c>
+      <c r="J297">
+        <v>1378.62</v>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2">
+        <v>45970</v>
+      </c>
+      <c r="B298">
+        <v>0</v>
+      </c>
+      <c r="C298">
+        <v>0</v>
+      </c>
+      <c r="D298">
+        <v>0</v>
+      </c>
+      <c r="E298">
+        <v>0</v>
+      </c>
+      <c r="F298">
+        <v>500</v>
+      </c>
+      <c r="G298">
+        <v>0</v>
+      </c>
+      <c r="H298">
+        <v>0</v>
+      </c>
+      <c r="I298">
+        <v>500</v>
+      </c>
+      <c r="J298">
+        <v>500</v>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2">
+        <v>45971</v>
+      </c>
+      <c r="B299">
+        <v>42519.82</v>
+      </c>
+      <c r="C299">
+        <v>4482.02</v>
+      </c>
+      <c r="D299">
+        <v>5876.82</v>
+      </c>
+      <c r="E299">
+        <v>41125.02</v>
+      </c>
+      <c r="F299">
+        <v>10477.6</v>
+      </c>
+      <c r="G299">
+        <v>0</v>
+      </c>
+      <c r="H299">
+        <v>0</v>
+      </c>
+      <c r="I299">
+        <v>10477.6</v>
+      </c>
+      <c r="J299">
+        <v>51602.62</v>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2">
+        <v>45972</v>
+      </c>
+      <c r="B300">
+        <v>53268.59</v>
+      </c>
+      <c r="C300">
+        <v>559.02</v>
+      </c>
+      <c r="D300">
+        <v>258</v>
+      </c>
+      <c r="E300">
+        <v>53569.60999999999</v>
+      </c>
+      <c r="F300">
+        <v>15587.51</v>
+      </c>
+      <c r="G300">
+        <v>0</v>
+      </c>
+      <c r="H300">
+        <v>311.65</v>
+      </c>
+      <c r="I300">
+        <v>15275.86</v>
+      </c>
+      <c r="J300">
+        <v>68845.47</v>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2">
+        <v>45973</v>
+      </c>
+      <c r="B301">
+        <v>72813.88</v>
+      </c>
+      <c r="C301">
+        <v>1365.19</v>
+      </c>
+      <c r="D301">
+        <v>240</v>
+      </c>
+      <c r="E301">
+        <v>73939.07000000001</v>
+      </c>
+      <c r="F301">
+        <v>11396.35</v>
+      </c>
+      <c r="G301">
+        <v>0</v>
+      </c>
+      <c r="H301">
+        <v>0</v>
+      </c>
+      <c r="I301">
+        <v>11396.35</v>
+      </c>
+      <c r="J301">
+        <v>85335.42000000001</v>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2">
+        <v>45974</v>
+      </c>
+      <c r="B302">
+        <v>67699.89999999999</v>
+      </c>
+      <c r="C302">
+        <v>630</v>
+      </c>
+      <c r="D302">
+        <v>760</v>
+      </c>
+      <c r="E302">
+        <v>67569.89999999999</v>
+      </c>
+      <c r="F302">
+        <v>8405.869999999999</v>
+      </c>
+      <c r="G302">
+        <v>0</v>
+      </c>
+      <c r="H302">
+        <v>0</v>
+      </c>
+      <c r="I302">
+        <v>8405.869999999999</v>
+      </c>
+      <c r="J302">
+        <v>75975.76999999999</v>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B303">
+        <v>35522.78</v>
+      </c>
+      <c r="C303">
+        <v>182.6</v>
+      </c>
+      <c r="D303">
+        <v>235.46</v>
+      </c>
+      <c r="E303">
+        <v>35469.92</v>
+      </c>
+      <c r="F303">
+        <v>15629.43</v>
+      </c>
+      <c r="G303">
+        <v>0</v>
+      </c>
+      <c r="H303">
+        <v>0</v>
+      </c>
+      <c r="I303">
+        <v>15629.43</v>
+      </c>
+      <c r="J303">
+        <v>51099.35</v>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2">
+        <v>45976</v>
+      </c>
+      <c r="B304">
+        <v>180</v>
+      </c>
+      <c r="C304">
+        <v>0</v>
+      </c>
+      <c r="D304">
+        <v>0</v>
+      </c>
+      <c r="E304">
+        <v>180</v>
+      </c>
+      <c r="F304">
+        <v>0</v>
+      </c>
+      <c r="G304">
+        <v>0</v>
+      </c>
+      <c r="H304">
+        <v>0</v>
+      </c>
+      <c r="I304">
+        <v>0</v>
+      </c>
+      <c r="J304">
+        <v>180</v>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2">
+        <v>45977</v>
+      </c>
+      <c r="B305">
+        <v>0</v>
+      </c>
+      <c r="C305">
+        <v>0</v>
+      </c>
+      <c r="D305">
+        <v>0</v>
+      </c>
+      <c r="E305">
+        <v>0</v>
+      </c>
+      <c r="F305">
+        <v>500</v>
+      </c>
+      <c r="G305">
+        <v>0</v>
+      </c>
+      <c r="H305">
+        <v>0</v>
+      </c>
+      <c r="I305">
+        <v>500</v>
+      </c>
+      <c r="J305">
+        <v>500</v>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B306">
+        <v>61422.78</v>
+      </c>
+      <c r="C306">
+        <v>858.4200000000001</v>
+      </c>
+      <c r="D306">
+        <v>238.46</v>
+      </c>
+      <c r="E306">
+        <v>62042.74</v>
+      </c>
+      <c r="F306">
+        <v>11965.48</v>
+      </c>
+      <c r="G306">
+        <v>0</v>
+      </c>
+      <c r="H306">
+        <v>0</v>
+      </c>
+      <c r="I306">
+        <v>11965.48</v>
+      </c>
+      <c r="J306">
+        <v>74008.22</v>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2">
+        <v>45979</v>
+      </c>
+      <c r="B307">
+        <v>73349.63</v>
+      </c>
+      <c r="C307">
+        <v>588.24</v>
+      </c>
+      <c r="D307">
+        <v>71.06</v>
+      </c>
+      <c r="E307">
+        <v>73866.81000000001</v>
+      </c>
+      <c r="F307">
+        <v>28651.21</v>
+      </c>
+      <c r="G307">
+        <v>0</v>
+      </c>
+      <c r="H307">
+        <v>0</v>
+      </c>
+      <c r="I307">
+        <v>28651.21</v>
+      </c>
+      <c r="J307">
+        <v>102518.02</v>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B308">
+        <v>61789.71</v>
+      </c>
+      <c r="C308">
+        <v>860.99</v>
+      </c>
+      <c r="D308">
+        <v>91</v>
+      </c>
+      <c r="E308">
+        <v>62559.7</v>
+      </c>
+      <c r="F308">
+        <v>34837.13</v>
+      </c>
+      <c r="G308">
+        <v>0</v>
+      </c>
+      <c r="H308">
+        <v>30</v>
+      </c>
+      <c r="I308">
+        <v>34807.13</v>
+      </c>
+      <c r="J308">
+        <v>97366.82999999999</v>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B309">
+        <v>57818.67</v>
+      </c>
+      <c r="C309">
+        <v>630.3100000000001</v>
+      </c>
+      <c r="D309">
+        <v>0</v>
+      </c>
+      <c r="E309">
+        <v>58448.98</v>
+      </c>
+      <c r="F309">
+        <v>8392.58</v>
+      </c>
+      <c r="G309">
+        <v>0</v>
+      </c>
+      <c r="H309">
+        <v>390</v>
+      </c>
+      <c r="I309">
+        <v>8002.58</v>
+      </c>
+      <c r="J309">
+        <v>66451.56</v>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B310">
+        <v>5441.31</v>
+      </c>
+      <c r="C310">
+        <v>30</v>
+      </c>
+      <c r="D310">
+        <v>0</v>
+      </c>
+      <c r="E310">
+        <v>5471.31</v>
+      </c>
+      <c r="F310">
+        <v>5613</v>
+      </c>
+      <c r="G310">
+        <v>0</v>
+      </c>
+      <c r="H310">
+        <v>0</v>
+      </c>
+      <c r="I310">
+        <v>5613</v>
+      </c>
+      <c r="J310">
+        <v>11084.31</v>
+      </c>
+      <c r="K310" t="inlineStr">
         <is>
           <t>SOJA</t>
         </is>
